--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,6 +1035,113 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131874298</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4774</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gatan, Gatan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504426</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6612371</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,6 +1142,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131914109</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101249</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504376</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6612366</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>131874298</v>
       </c>
       <c r="B5" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>131914109</v>
       </c>
       <c r="B6" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,7 +1148,7 @@
         <v>131914109</v>
       </c>
       <c r="B6" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,6 +1245,115 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132122898</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58069</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504386</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6612519</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>131914109</v>
       </c>
       <c r="B6" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>132122898</v>
       </c>
       <c r="B7" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>131914109</v>
       </c>
       <c r="B6" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>132122898</v>
       </c>
       <c r="B7" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>131914109</v>
       </c>
       <c r="B6" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>132122898</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>131914109</v>
       </c>
       <c r="B6" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>132122898</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>132122898</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1601,6 +1601,498 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133718908</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504364</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6612353</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133719431</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504358</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6612573</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133718914</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504364</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6612353</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133718936</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>504445</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6612403</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>133408387</v>
       </c>
       <c r="B8" t="n">
-        <v>107624</v>
+        <v>107626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>133408387</v>
       </c>
       <c r="B8" t="n">
-        <v>107626</v>
+        <v>107634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2093,6 +2093,129 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134081771</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504445</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6612366</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>133408387</v>
       </c>
       <c r="B8" t="n">
-        <v>107634</v>
+        <v>107662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>133407850</v>
       </c>
       <c r="B9" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>133718908</v>
       </c>
       <c r="B10" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>133719431</v>
       </c>
       <c r="B11" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>133718914</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>133718936</v>
       </c>
       <c r="B13" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>134081771</v>
       </c>
       <c r="B14" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>133408387</v>
       </c>
       <c r="B8" t="n">
-        <v>107662</v>
+        <v>107672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>133407850</v>
       </c>
       <c r="B9" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>133718908</v>
       </c>
       <c r="B10" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>133719431</v>
       </c>
       <c r="B11" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>133718914</v>
       </c>
       <c r="B12" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>133718936</v>
       </c>
       <c r="B13" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>134081771</v>
       </c>
       <c r="B14" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>133408387</v>
       </c>
       <c r="B8" t="n">
-        <v>107672</v>
+        <v>107673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97080141</v>
+        <v>98207928</v>
       </c>
       <c r="B2" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100943</v>
+        <v>720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Leja yta 1:6, Vstm</t>
+          <t>Lejaskogens naturreservat, norr om, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504426.7564176009</v>
+        <v>504331</v>
       </c>
       <c r="R2" t="n">
-        <v>6612446.201182278</v>
+        <v>6612377</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,32 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
     </row>
@@ -799,16 +784,11 @@
         <v>98207926</v>
       </c>
       <c r="B3" t="n">
-        <v>90655</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504262.7940904821</v>
+        <v>504263</v>
       </c>
       <c r="R3" t="n">
-        <v>6612365.134466335</v>
+        <v>6612365</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,16 +890,11 @@
         <v>98207927</v>
       </c>
       <c r="B4" t="n">
-        <v>90655</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504407.6053563274</v>
+        <v>504407</v>
       </c>
       <c r="R4" t="n">
-        <v>6612369.851553588</v>
+        <v>6612370</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -990,19 +955,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131874298</v>
+        <v>131914162</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,37 +1004,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gatan, Gatan, Vstm</t>
+          <t>200 m O Smedsjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504426</v>
+        <v>504376</v>
       </c>
       <c r="R5" t="n">
-        <v>6612371</v>
+        <v>6612363</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1062,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig. Rik mossflora. Stort område med källflöden, rörligt markvatten och översilning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,28 +1081,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131914109</v>
+        <v>133407963</v>
       </c>
       <c r="B6" t="n">
-        <v>101323</v>
+        <v>96533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,17 +1135,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>200 m O Smedsjön, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504376</v>
+        <v>504360</v>
       </c>
       <c r="R6" t="n">
-        <v>6612366</v>
+        <v>6612415</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,12 +1169,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,75 +1197,72 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132122898</v>
+        <v>131874298</v>
       </c>
       <c r="B7" t="n">
-        <v>58113</v>
+        <v>4776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Gatan, Gatan, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504386</v>
+        <v>504426</v>
       </c>
       <c r="R7" t="n">
-        <v>6612519</v>
+        <v>6612371</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,12 +1286,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,58 +1316,58 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133408387</v>
+        <v>134381659</v>
       </c>
       <c r="B8" t="n">
-        <v>107673</v>
+        <v>58519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219686</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504425</v>
+        <v>504302</v>
       </c>
       <c r="R8" t="n">
-        <v>6612573</v>
+        <v>6612491</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,17 +1405,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1457,7 +1429,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133407850</v>
+        <v>133407911</v>
       </c>
       <c r="B9" t="n">
-        <v>58461</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,21 +1462,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1527,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504380</v>
+        <v>504320</v>
       </c>
       <c r="R9" t="n">
-        <v>6612529</v>
+        <v>6612489</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1603,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718908</v>
+        <v>133718936</v>
       </c>
       <c r="B10" t="n">
-        <v>58461</v>
+        <v>58260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,21 +1585,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1650,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504364</v>
+        <v>504445</v>
       </c>
       <c r="R10" t="n">
-        <v>6612353</v>
+        <v>6612403</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1849,32 +1820,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133718914</v>
+        <v>134081783</v>
       </c>
       <c r="B12" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1896,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504364</v>
+        <v>504424</v>
       </c>
       <c r="R12" t="n">
-        <v>6612353</v>
+        <v>6612605</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1926,7 +1897,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1936,12 +1907,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,7 +1943,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133718936</v>
+        <v>134082041</v>
       </c>
       <c r="B13" t="n">
         <v>58260</v>
@@ -2019,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504445</v>
+        <v>504282</v>
       </c>
       <c r="R13" t="n">
-        <v>6612403</v>
+        <v>6612406</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2049,7 +2020,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2059,12 +2030,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,32 +2066,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134081771</v>
+        <v>134381684</v>
       </c>
       <c r="B14" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2142,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504445</v>
+        <v>504418</v>
       </c>
       <c r="R14" t="n">
-        <v>6612366</v>
+        <v>6612570</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2172,22 +2143,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,7 +2189,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134381684</v>
+        <v>134381783</v>
       </c>
       <c r="B15" t="n">
         <v>58260</v>
@@ -2265,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504418</v>
+        <v>504459</v>
       </c>
       <c r="R15" t="n">
-        <v>6612570</v>
+        <v>6612553</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2334,6 +2305,2406 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133718914</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>504364</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6612353</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133719177</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>504321</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6612508</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134081771</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504445</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612366</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134081776</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504445</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6612489</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134381653</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504250</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6612387</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134381672</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504312</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6612541</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133407850</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>504380</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6612529</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133407956</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>504360</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6612415</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133718908</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>504364</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6612353</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134082031</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504334</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6612599</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134382003</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>504418</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6612609</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132122898</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>504386</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6612519</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133408387</v>
+      </c>
+      <c r="B28" t="n">
+        <v>107690</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504425</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6612573</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133407921</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504320</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6612489</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133719224</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>504321</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6612508</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Noterad spridd i öppnare delar.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134082048</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104878</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221178</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bäckbräsma</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cardamine amara</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>504348</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6612393</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133407929</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>504320</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6612489</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131914109</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>504376</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6612366</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133407939</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>504320</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6612489</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133407932</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>504320</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6612489</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8178-2026 artfynd.xlsx
+++ b/artfynd/A 8178-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98207928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98207926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98207927</t>
         </is>
       </c>
     </row>
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914162</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407963</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131874298</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381659</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1571,6 +1611,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407911</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718936</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1817,6 +1867,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719431</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081783</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082041</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2186,6 +2251,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2309,6 +2379,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381783</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2430,6 +2505,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718914</t>
         </is>
       </c>
     </row>
@@ -2551,6 +2631,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719177</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2674,6 +2759,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081771</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2797,6 +2887,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081776</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2920,6 +3015,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381653</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3043,6 +3143,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381672</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3166,6 +3271,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407850</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3289,6 +3399,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407956</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3412,6 +3527,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718908</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3535,6 +3655,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082031</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3658,6 +3783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134382003</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3767,6 +3897,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122898</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3889,6 +4024,11 @@
       <c r="AY28" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408387</t>
         </is>
       </c>
     </row>
@@ -4012,6 +4152,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407921</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4133,6 +4278,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719224</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4254,6 +4404,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082048</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4375,6 +4530,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407929</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4477,6 +4637,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914109</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4593,6 +4758,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407939</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4709,8 +4879,49 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407932</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>